--- a/data/trans_orig/dukeAFECT-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/dukeAFECT-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de apoyo afectivo (Duke)</t>
+          <t>Puntuación media de la escala de apoyo afectivo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,06</t>
+          <t>16,63; 17,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,2; 17,59</t>
+          <t>17,21; 17,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,58; 17,02</t>
+          <t>16,59; 17,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,36; 16,97</t>
+          <t>16,35; 16,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,29; 16,68</t>
+          <t>16,27; 16,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,09; 17,41</t>
+          <t>17,08; 17,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 16,66</t>
+          <t>16,26; 16,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,22; 16,6</t>
+          <t>16,21; 16,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,2; 17,44</t>
+          <t>17,19; 17,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 16,74</t>
+          <t>16,46; 16,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,67</t>
+          <t>16,33; 16,68</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,74; 17,98</t>
+          <t>17,75; 18,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 18,04</t>
+          <t>17,82; 18,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,47 +871,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,6</t>
+          <t>17,66; 18,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 17,67</t>
+          <t>17,37; 17,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,69</t>
+          <t>17,45; 17,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,0; 17,23</t>
+          <t>16,99; 17,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 17,76</t>
+          <t>16,79; 17,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,61; 17,8</t>
+          <t>17,6; 17,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 17,85</t>
+          <t>17,67; 17,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 17,23</t>
+          <t>17,06; 17,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,33; 18,02</t>
+          <t>17,4; 18,04</t>
         </is>
       </c>
     </row>
@@ -996,37 +996,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,61; 18,09</t>
+          <t>17,6; 18,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,82; 18,33</t>
+          <t>17,79; 18,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 17,99</t>
+          <t>17,6; 18,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 18,3</t>
+          <t>17,88; 18,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,68; 18,21</t>
+          <t>17,68; 18,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 18,49</t>
+          <t>18,09; 18,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,49; 17,92</t>
+          <t>17,49; 17,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,22 +1036,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,73; 18,07</t>
+          <t>17,73; 18,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,02; 18,34</t>
+          <t>18,01; 18,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,61; 17,91</t>
+          <t>17,62; 17,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 18,32</t>
+          <t>18,05; 18,31</t>
         </is>
       </c>
     </row>
@@ -1136,32 +1136,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,65</t>
+          <t>17,44; 17,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,71; 17,9</t>
+          <t>17,72; 17,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 17,29</t>
+          <t>17,1; 17,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,34</t>
+          <t>17,58; 18,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,28</t>
+          <t>17,07; 17,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 17,65</t>
+          <t>17,46; 17,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,58</t>
+          <t>16,92; 17,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,61; 17,74</t>
+          <t>17,62; 17,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 17,18</t>
+          <t>17,05; 17,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,35; 17,83</t>
+          <t>17,37; 17,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeAFECT-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/dukeAFECT-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,66</t>
+          <t>16,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>16,32</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,51</t>
+          <t>16,41</t>
         </is>
       </c>
     </row>
@@ -716,32 +716,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,63; 17,05</t>
+          <t>16,64; 17,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,58</t>
+          <t>17,21; 17,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 17,0</t>
+          <t>16,57; 16,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,35; 16,96</t>
+          <t>16,19; 16,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,27; 16,66</t>
+          <t>16,27; 16,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 17,4</t>
+          <t>17,08; 17,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,21; 16,62</t>
+          <t>16,1; 16,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,51; 16,79</t>
+          <t>16,51; 16,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 17,44</t>
+          <t>17,2; 17,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,46; 16,77</t>
+          <t>16,44; 16,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,68</t>
+          <t>16,23; 16,58</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,95</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,44</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>17,55</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 18,0</t>
+          <t>17,74; 17,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 18,05</t>
+          <t>17,81; 18,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 17,3</t>
+          <t>17,06; 17,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,73</t>
+          <t>17,46; 17,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,37 +881,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,45; 17,7</t>
+          <t>17,44; 17,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,23</t>
+          <t>17,0; 17,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 17,79</t>
+          <t>17,37; 17,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,6; 17,79</t>
+          <t>17,61; 17,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 17,85</t>
+          <t>17,68; 17,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 17,24</t>
+          <t>17,07; 17,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,4; 18,04</t>
+          <t>17,46; 17,64</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,09</t>
+          <t>18,07</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,28</t>
+          <t>18,24</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,19</t>
+          <t>18,16</t>
         </is>
       </c>
     </row>
@@ -996,32 +996,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 18,09</t>
+          <t>17,58; 18,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,79; 18,29</t>
+          <t>17,82; 18,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 18,01</t>
+          <t>17,6; 18,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 18,29</t>
+          <t>17,82; 18,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,68; 18,19</t>
+          <t>17,69; 18,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,09; 18,5</t>
+          <t>18,12; 18,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,11; 18,43</t>
+          <t>18,08; 18,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,73; 18,09</t>
+          <t>17,72; 18,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,01; 18,33</t>
+          <t>18,02; 18,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,62; 17,91</t>
+          <t>17,62; 17,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 18,31</t>
+          <t>18,01; 18,28</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,79</t>
+          <t>17,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>17,39</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,44; 17,64</t>
+          <t>17,45; 17,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,22 +1146,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,29</t>
+          <t>17,11; 17,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,58; 18,25</t>
+          <t>17,42; 17,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,29</t>
+          <t>17,06; 17,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 17,64</t>
+          <t>17,45; 17,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,27 +1171,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 17,58</t>
+          <t>17,3; 17,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,28; 17,43</t>
+          <t>17,28; 17,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 17,75</t>
+          <t>17,61; 17,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 17,18</t>
+          <t>17,04; 17,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 17,83</t>
+          <t>17,37; 17,52</t>
         </is>
       </c>
     </row>
